--- a/강의예제/6장_자동화를_위한_표와_피벗_테이블/6장_복습.xlsx
+++ b/강의예제/6장_자동화를_위한_표와_피벗_테이블/6장_복습.xlsx
@@ -1150,7 +1150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:G11"/>
+  <dimension ref="B1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1172,7 +1172,7 @@
     <row r="2">
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>아래 값으로 이익률을 두 방식으로 내 보고, 차이를 적으세요.</t>
+          <t>이익률을 두 방식으로 내 보고, 계산 항목이 총합계를 어떻게 바꾸는지 적으세요.</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,9 @@
       <c r="G4" s="7" t="inlineStr">
         <is>
           <t>계산 필드는 합계를 먼저 내고 나눕니다.
-계산 항목은 줄마다 나눈 값을 더합니다.
+원본에 만든 비율 열을 「합계」로 넣으면 줄마다 나눈 값을 더합니다.
+계산 항목은 한 필드 안의 항목끼리 계산하고,
+그 줄이 총합계에 같이 더해집니다.
 둘이 얼마나 다른지 직접 계산해 보세요.
 매출 합계 64,000 · 이익 합계 4,420</t>
         </is>
@@ -1255,7 +1257,7 @@
     <row r="10">
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>② 계산 항목 방식 (줄별 이익률을 더함)</t>
+          <t>② 원본에 이익률 열을 만들어 합계로 (줄별 이익률을 더함)</t>
         </is>
       </c>
       <c r="C10" s="13" t="n"/>
@@ -1272,10 +1274,21 @@
       <c r="D11" s="11" t="n"/>
       <c r="E11" s="14" t="n"/>
     </row>
+    <row r="12">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>④ 계산 항목 「2023−2022 차이」 를 넣으면 매출 총합계는?</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="6" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
     <mergeCell ref="B11:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1413,12 +1426,12 @@
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
-          <t>줄별: 5.0% · 17.0% · 6.1%   ① 6.9% (맞음)   ② 28.0% (틀림)   ③ ①</t>
+          <t>줄별: 5.0% · 17.0% · 6.1%   ① 6.9% (맞음)   ② 28.0% (틀림)   ③ ①   ④ 82,000 (맞는 값 64,000 — 차이 18,000 까지 더해짐)</t>
         </is>
       </c>
       <c r="E8" s="18" t="inlineStr">
         <is>
-          <t>비율의 합은 아무 뜻이 없습니다. 그런데 피벗은 그 값을 자신 있게 내놓습니다.</t>
+          <t>비율의 합은 아무 뜻이 없습니다. 계산 항목 줄도 총합계에 더해집니다. 피벗은 둘 다 오류 없이 자신 있게 내놓습니다.</t>
         </is>
       </c>
     </row>
